--- a/data_raw/re_A030C_住宅商品房平均销售价格_元_平方米.xlsx
+++ b/data_raw/re_A030C_住宅商品房平均销售价格_元_平方米.xlsx
@@ -1,216 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>住宅商品房平均销售价格(元/平方米)</t>
-  </si>
-  <si>
-    <t>上海</t>
-  </si>
-  <si>
-    <t>乌鲁木齐</t>
-  </si>
-  <si>
-    <t>兰州</t>
-  </si>
-  <si>
-    <t>北京</t>
-  </si>
-  <si>
-    <t>南京</t>
-  </si>
-  <si>
-    <t>南宁</t>
-  </si>
-  <si>
-    <t>南昌</t>
-  </si>
-  <si>
-    <t>厦门</t>
-  </si>
-  <si>
-    <t>合肥</t>
-  </si>
-  <si>
-    <t>呼和浩特</t>
-  </si>
-  <si>
-    <t>哈尔滨</t>
-  </si>
-  <si>
-    <t>大连</t>
-  </si>
-  <si>
-    <t>天津</t>
-  </si>
-  <si>
-    <t>太原</t>
-  </si>
-  <si>
-    <t>宁波</t>
-  </si>
-  <si>
-    <t>广州</t>
-  </si>
-  <si>
-    <t>成都</t>
-  </si>
-  <si>
-    <t>拉萨</t>
-  </si>
-  <si>
-    <t>昆明</t>
-  </si>
-  <si>
-    <t>杭州</t>
-  </si>
-  <si>
-    <t>武汉</t>
-  </si>
-  <si>
-    <t>沈阳</t>
-  </si>
-  <si>
-    <t>济南</t>
-  </si>
-  <si>
-    <t>海口</t>
-  </si>
-  <si>
-    <t>深圳</t>
-  </si>
-  <si>
-    <t>石家庄</t>
-  </si>
-  <si>
-    <t>福州</t>
-  </si>
-  <si>
-    <t>西宁</t>
-  </si>
-  <si>
-    <t>西安</t>
-  </si>
-  <si>
-    <t>贵阳</t>
-  </si>
-  <si>
-    <t>郑州</t>
-  </si>
-  <si>
-    <t>重庆</t>
-  </si>
-  <si>
-    <t>银川</t>
-  </si>
-  <si>
-    <t>长春</t>
-  </si>
-  <si>
-    <t>长沙</t>
-  </si>
-  <si>
-    <t>青岛</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -225,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -541,2251 +420,2424 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>住宅商品房平均销售价格(元/平方米)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>7039.00012674482</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>8252.999954714211</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>8115</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>12364</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>14290</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>13565.8338087778</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>13869.8832696943</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>16192</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>16415</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>21501</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>25910</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>24866</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>28981.1057057744</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>32926</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>36741</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>40974</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>44430</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>45997</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>47223</v>
       </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3">
+      <c r="U2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>乌鲁木齐</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>2020.94040134285</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>2528.46949239446</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>3031</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>3285</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>4265</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>4969.78223374701</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>5255.03993226132</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>5858</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>5758</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>6142</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>5829</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>6188</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>7757.03433983886</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>8728</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>7959</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>8013</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>8025</v>
       </c>
-      <c r="S3">
+      <c r="S3" t="n">
         <v>8586</v>
       </c>
-      <c r="T3">
+      <c r="T3" t="n">
         <v>8828</v>
       </c>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4">
+      <c r="U3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>2514.68109415267</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>2919.61601709794</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>3062</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>3499</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>4065</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>4229.09439373699</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>5420.66977882057</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>5520</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>5860</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>6089</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>6162</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>7137</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>7231.86717146711</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>7332</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>8281</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>7795</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>7830</v>
       </c>
-      <c r="S4">
+      <c r="S4" t="n">
         <v>8453</v>
       </c>
-      <c r="T4">
+      <c r="T4" t="n">
         <v>7886</v>
       </c>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5">
+      <c r="U4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>7375.40892875089</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>10661.2447918826</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>11648</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>13224</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>17151</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>15517.898842159</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>16553.4774560654</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>17854</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>18499</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>22300</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>28489</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>34117</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>37420.1885411996</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>38433</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>42684</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>46941</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>47784</v>
       </c>
-      <c r="S5">
+      <c r="S5" t="n">
         <v>46783</v>
       </c>
-      <c r="T5">
+      <c r="T5" t="n">
         <v>38673</v>
       </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6">
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>4270.36151369393</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>5010.94159326319</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>4808</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>6893</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>9227</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>8414.615358292551</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>9674.8384999871</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>11078</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>10964</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>11260</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>17884</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>15259</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>19708.3270874809</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>19428</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>25175</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>27938</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>27826</v>
       </c>
-      <c r="S6">
+      <c r="S6" t="n">
         <v>23643</v>
       </c>
-      <c r="T6">
+      <c r="T6" t="n">
         <v>17946</v>
       </c>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7">
+      <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>南宁</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>2656.11421743505</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>3273.37728296064</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>3726</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>4463</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>4942</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>4995.88887785476</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>5618.65400427161</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>6155</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>6103</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>6229</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>6767</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>7700</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>7697.26554990307</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>8574</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>9200</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>8960</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>8927</v>
       </c>
-      <c r="S7">
+      <c r="S7" t="n">
         <v>9917</v>
       </c>
-      <c r="T7">
+      <c r="T7" t="n">
         <v>9358</v>
       </c>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8">
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>3053.13200720916</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>3508.69513648456</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>3361</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>3637</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>4331</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>5322.65888341428</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>5879.98985441761</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>6639</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>6225</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>6955</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>7707</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>8106</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>8275.87187617107</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>9355</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>10866</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>10576</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>10824</v>
       </c>
-      <c r="S8">
+      <c r="S8" t="n">
         <v>10733</v>
       </c>
-      <c r="T8">
+      <c r="T8" t="n">
         <v>10073</v>
       </c>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>厦门</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>6600.7259299402</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>8907.01840311508</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>8940</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>8935</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>11590</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>13422.5945604694</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>12953.375751193</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>14551</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>17778</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>18928</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>25251</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>28053</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>33715.4275248665</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>33830</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>33779</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>31425</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>27523</v>
       </c>
-      <c r="S9">
+      <c r="S9" t="n">
         <v>31054</v>
       </c>
-      <c r="T9">
+      <c r="T9" t="n">
         <v>18609</v>
       </c>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10">
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>2873.77562129772</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>3153.79659910839</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>3425</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>4095</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>5502</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>5607.54757697809</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>5754.31315325584</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>6084</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>6917</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>7512</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>9312</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>11442</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>13068.6339121561</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>14086</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>15265</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>14443</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>13476</v>
       </c>
-      <c r="S10">
+      <c r="S10" t="n">
         <v>15530</v>
       </c>
-      <c r="T10">
+      <c r="T10" t="n">
         <v>13011</v>
       </c>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11">
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>2175.71425992175</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>2458.81989508033</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>2511</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>3248</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>3650</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>4073.31898759717</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>4798.16579750107</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>4631</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>5153</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>4946</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>5196</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>5662</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>8251.24024478992</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>10029</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>11066</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>11314</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>11100</v>
       </c>
-      <c r="S11">
+      <c r="S11" t="n">
         <v>10845</v>
       </c>
-      <c r="T11">
+      <c r="T11" t="n">
         <v>10522</v>
       </c>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12">
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>2502.86018066989</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>2942.74480184291</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>3515</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>4146</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>5196</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>5216.66390765998</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>5112.84802412843</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>5884</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>5751</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>6124</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>6338</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>7861</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>8931.924451419311</v>
       </c>
-      <c r="O12">
+      <c r="O12" t="n">
         <v>9780</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>9460</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="n">
         <v>8778</v>
       </c>
-      <c r="R12">
+      <c r="R12" t="n">
         <v>8327</v>
       </c>
-      <c r="S12">
+      <c r="S12" t="n">
         <v>8434</v>
       </c>
-      <c r="T12">
+      <c r="T12" t="n">
         <v>8458</v>
       </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13">
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>大连</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>4256.41662387514</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>5417.28211619645</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>5617</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>6175</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>6759</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>7928.98018138913</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>7583.96652043558</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>7859</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>8921</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>8711</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>9119</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>10019</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>11432.5522143416</v>
       </c>
-      <c r="O13">
+      <c r="O13" t="n">
         <v>12041</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>13501</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="n">
         <v>14080</v>
       </c>
-      <c r="R13">
+      <c r="R13" t="n">
         <v>12771</v>
       </c>
-      <c r="S13">
+      <c r="S13" t="n">
         <v>11899</v>
       </c>
-      <c r="T13">
+      <c r="T13" t="n">
         <v>11073</v>
       </c>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14">
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>4649.24731983301</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>5575.71537172965</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>5598</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>6605</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>7940</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>8547.63620425185</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="n">
         <v>8009.5807657414</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="n">
         <v>8390</v>
       </c>
-      <c r="J14">
+      <c r="J14" t="n">
         <v>8828</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="n">
         <v>9931</v>
       </c>
-      <c r="L14">
+      <c r="L14" t="n">
         <v>12870</v>
       </c>
-      <c r="M14">
+      <c r="M14" t="n">
         <v>15139</v>
       </c>
-      <c r="N14">
+      <c r="N14" t="n">
         <v>15924.2605226787</v>
       </c>
-      <c r="O14">
+      <c r="O14" t="n">
         <v>15423</v>
       </c>
-      <c r="P14">
+      <c r="P14" t="n">
         <v>16391</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" t="n">
         <v>16370</v>
       </c>
-      <c r="R14">
+      <c r="R14" t="n">
         <v>15874</v>
       </c>
-      <c r="S14">
+      <c r="S14" t="n">
         <v>16324</v>
       </c>
-      <c r="T14">
+      <c r="T14" t="n">
         <v>14967</v>
       </c>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15">
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>3156.26061378944</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>3560.53712963634</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>3743</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>4499</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>7088</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>6517.46624190345</v>
       </c>
-      <c r="H15">
+      <c r="H15" t="n">
         <v>6404.74296550231</v>
       </c>
-      <c r="I15">
+      <c r="I15" t="n">
         <v>6668</v>
       </c>
-      <c r="J15">
+      <c r="J15" t="n">
         <v>7155</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="n">
         <v>7303</v>
       </c>
-      <c r="L15">
+      <c r="L15" t="n">
         <v>7348</v>
       </c>
-      <c r="M15">
+      <c r="M15" t="n">
         <v>8827</v>
       </c>
-      <c r="N15">
+      <c r="N15" t="n">
         <v>10840.4853698825</v>
       </c>
-      <c r="O15">
+      <c r="O15" t="n">
         <v>11136</v>
       </c>
-      <c r="P15">
+      <c r="P15" t="n">
         <v>10815</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" t="n">
         <v>10395</v>
       </c>
-      <c r="R15">
+      <c r="R15" t="n">
         <v>9848</v>
       </c>
-      <c r="S15">
+      <c r="S15" t="n">
         <v>10105</v>
       </c>
-      <c r="T15">
+      <c r="T15" t="n">
         <v>11424</v>
       </c>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16">
+      <c r="U15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>5105.07781837022</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>6097.16640294417</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>6843</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>9068</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>11669</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>11285.6393657342</v>
       </c>
-      <c r="H16">
+      <c r="H16" t="n">
         <v>11385.2467432137</v>
       </c>
-      <c r="I16">
+      <c r="I16" t="n">
         <v>11405</v>
       </c>
-      <c r="J16">
+      <c r="J16" t="n">
         <v>10890</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="n">
         <v>11022</v>
       </c>
-      <c r="L16">
+      <c r="L16" t="n">
         <v>11738</v>
       </c>
-      <c r="M16">
+      <c r="M16" t="n">
         <v>14145</v>
       </c>
-      <c r="N16">
+      <c r="N16" t="n">
         <v>16201.5778051833</v>
       </c>
-      <c r="O16">
+      <c r="O16" t="n">
         <v>15956</v>
       </c>
-      <c r="P16">
+      <c r="P16" t="n">
         <v>17657</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" t="n">
         <v>21152</v>
       </c>
-      <c r="R16">
+      <c r="R16" t="n">
         <v>19136</v>
       </c>
-      <c r="S16">
+      <c r="S16" t="n">
         <v>19546</v>
       </c>
-      <c r="T16">
+      <c r="T16" t="n">
         <v>17224</v>
       </c>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="A17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17">
+      <c r="U16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>6152.16776162855</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>8439.06216406959</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>8781</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>8988</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>10615</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>10925.8404174207</v>
       </c>
-      <c r="H17">
+      <c r="H17" t="n">
         <v>12000.8839965434</v>
       </c>
-      <c r="I17">
+      <c r="I17" t="n">
         <v>13954</v>
       </c>
-      <c r="J17">
+      <c r="J17" t="n">
         <v>14739</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="n">
         <v>14083</v>
       </c>
-      <c r="L17">
+      <c r="L17" t="n">
         <v>16346</v>
       </c>
-      <c r="M17">
+      <c r="M17" t="n">
         <v>17685</v>
       </c>
-      <c r="N17">
+      <c r="N17" t="n">
         <v>21581.7793133817</v>
       </c>
-      <c r="O17">
+      <c r="O17" t="n">
         <v>24015</v>
       </c>
-      <c r="P17">
+      <c r="P17" t="n">
         <v>27112</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" t="n">
         <v>30580</v>
       </c>
-      <c r="R17">
+      <c r="R17" t="n">
         <v>29455</v>
       </c>
-      <c r="S17">
+      <c r="S17" t="n">
         <v>32433</v>
       </c>
-      <c r="T17">
+      <c r="T17" t="n">
         <v>31427</v>
       </c>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18">
+      <c r="U17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>3498.95366613567</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>4198.2754419511</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>4778</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>4864</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>5827</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="n">
         <v>6360.88674294508</v>
       </c>
-      <c r="H18">
+      <c r="H18" t="n">
         <v>6678.46446417192</v>
       </c>
-      <c r="I18">
+      <c r="I18" t="n">
         <v>6708</v>
       </c>
-      <c r="J18">
+      <c r="J18" t="n">
         <v>6536</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="n">
         <v>6584</v>
       </c>
-      <c r="L18">
+      <c r="L18" t="n">
         <v>7377</v>
       </c>
-      <c r="M18">
+      <c r="M18" t="n">
         <v>8595</v>
       </c>
-      <c r="N18">
+      <c r="N18" t="n">
         <v>9783.15594508948</v>
       </c>
-      <c r="O18">
+      <c r="O18" t="n">
         <v>11729</v>
       </c>
-      <c r="P18">
+      <c r="P18" t="n">
         <v>13231</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" t="n">
         <v>14713</v>
       </c>
-      <c r="R18">
+      <c r="R18" t="n">
         <v>16811</v>
       </c>
-      <c r="S18">
+      <c r="S18" t="n">
         <v>19517</v>
       </c>
-      <c r="T18">
+      <c r="T18" t="n">
         <v>19028</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
-      <c r="A19" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20">
+      <c r="U18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>拉萨</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>2732.8449048755</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>2993.8623853626</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>3499</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>3586</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>3405</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>4550.12113240319</v>
       </c>
-      <c r="H20">
+      <c r="H20" t="n">
         <v>5404.89928036623</v>
       </c>
-      <c r="I20">
+      <c r="I20" t="n">
         <v>5615</v>
       </c>
-      <c r="J20">
+      <c r="J20" t="n">
         <v>6067</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="n">
         <v>7178</v>
       </c>
-      <c r="L20">
+      <c r="L20" t="n">
         <v>6851</v>
       </c>
-      <c r="M20">
+      <c r="M20" t="n">
         <v>8197</v>
       </c>
-      <c r="N20">
+      <c r="N20" t="n">
         <v>11085.4783733039</v>
       </c>
-      <c r="O20">
+      <c r="O20" t="n">
         <v>12123</v>
       </c>
-      <c r="P20">
+      <c r="P20" t="n">
         <v>12212</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" t="n">
         <v>12353</v>
       </c>
-      <c r="R20">
+      <c r="R20" t="n">
         <v>11344</v>
       </c>
-      <c r="S20">
+      <c r="S20" t="n">
         <v>11005</v>
       </c>
-      <c r="T20">
+      <c r="T20" t="n">
         <v>10069</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21">
+      <c r="U20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>5967.44151365842</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>7431.76433772444</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>8211</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>10613</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>14259</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>12748.622758781</v>
       </c>
-      <c r="H21">
+      <c r="H21" t="n">
         <v>13291.6547542322</v>
       </c>
-      <c r="I21">
+      <c r="I21" t="n">
         <v>14679</v>
       </c>
-      <c r="J21">
+      <c r="J21" t="n">
         <v>14035</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="n">
         <v>14748</v>
       </c>
-      <c r="L21">
+      <c r="L21" t="n">
         <v>16211</v>
       </c>
-      <c r="M21">
+      <c r="M21" t="n">
         <v>21225</v>
       </c>
-      <c r="N21">
+      <c r="N21" t="n">
         <v>24360.2008781083</v>
       </c>
-      <c r="O21">
+      <c r="O21" t="n">
         <v>26522</v>
       </c>
-      <c r="P21">
+      <c r="P21" t="n">
         <v>27448</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" t="n">
         <v>29781</v>
       </c>
-      <c r="R21">
+      <c r="R21" t="n">
         <v>33669</v>
       </c>
-      <c r="S21">
+      <c r="S21" t="n">
         <v>33047</v>
       </c>
-      <c r="T21">
+      <c r="T21" t="n">
         <v>30703</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22">
+      <c r="U21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>3535.26206290302</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>4515.75965565912</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>4681</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>5199</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>5550</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>6675.9899070129</v>
       </c>
-      <c r="H22">
+      <c r="H22" t="n">
         <v>6895.35101482145</v>
       </c>
-      <c r="I22">
+      <c r="I22" t="n">
         <v>7238</v>
       </c>
-      <c r="J22">
+      <c r="J22" t="n">
         <v>7399</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="n">
         <v>8404</v>
       </c>
-      <c r="L22">
+      <c r="L22" t="n">
         <v>9819</v>
       </c>
-      <c r="M22">
+      <c r="M22" t="n">
         <v>11453</v>
       </c>
-      <c r="N22">
+      <c r="N22" t="n">
         <v>12678.4774088261</v>
       </c>
-      <c r="O22">
+      <c r="O22" t="n">
         <v>13834</v>
       </c>
-      <c r="P22">
+      <c r="P22" t="n">
         <v>14672</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" t="n">
         <v>15504</v>
       </c>
-      <c r="R22">
+      <c r="R22" t="n">
         <v>14776</v>
       </c>
-      <c r="S22">
+      <c r="S22" t="n">
         <v>14883</v>
       </c>
-      <c r="T22">
+      <c r="T22" t="n">
         <v>13571</v>
       </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23">
+      <c r="U22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>3184.00023082624</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>3535.75051522055</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>3856</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>4196</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>5109</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>5612.95679536556</v>
       </c>
-      <c r="H23">
+      <c r="H23" t="n">
         <v>5989.45115748004</v>
       </c>
-      <c r="I23">
+      <c r="I23" t="n">
         <v>6074</v>
       </c>
-      <c r="J23">
+      <c r="J23" t="n">
         <v>5865</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="n">
         <v>6416</v>
       </c>
-      <c r="L23">
+      <c r="L23" t="n">
         <v>6838</v>
       </c>
-      <c r="M23">
+      <c r="M23" t="n">
         <v>7944</v>
       </c>
-      <c r="N23">
+      <c r="N23" t="n">
         <v>8680.113710015839</v>
       </c>
-      <c r="O23">
+      <c r="O23" t="n">
         <v>10251</v>
       </c>
-      <c r="P23">
+      <c r="P23" t="n">
         <v>11617</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" t="n">
         <v>11997</v>
       </c>
-      <c r="R23">
+      <c r="R23" t="n">
         <v>11005</v>
       </c>
-      <c r="S23">
+      <c r="S23" t="n">
         <v>11219</v>
       </c>
-      <c r="T23">
+      <c r="T23" t="n">
         <v>10849</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24">
+      <c r="U23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>3318.897582612</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>3719.6220736292</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>4155</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>4790</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>6100</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>6663.88630439938</v>
       </c>
-      <c r="H24">
+      <c r="H24" t="n">
         <v>6650.5649472826</v>
       </c>
-      <c r="I24">
+      <c r="I24" t="n">
         <v>7013</v>
       </c>
-      <c r="J24">
+      <c r="J24" t="n">
         <v>7158</v>
       </c>
-      <c r="K24">
+      <c r="K24" t="n">
         <v>7527</v>
       </c>
-      <c r="L24">
+      <c r="L24" t="n">
         <v>8405</v>
       </c>
-      <c r="M24">
+      <c r="M24" t="n">
         <v>9712</v>
       </c>
-      <c r="N24">
+      <c r="N24" t="n">
         <v>12161.452730012</v>
       </c>
-      <c r="O24">
+      <c r="O24" t="n">
         <v>11947</v>
       </c>
-      <c r="P24">
+      <c r="P24" t="n">
         <v>12282</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" t="n">
         <v>13241</v>
       </c>
-      <c r="R24">
+      <c r="R24" t="n">
         <v>13469</v>
       </c>
-      <c r="S24">
+      <c r="S24" t="n">
         <v>14758</v>
       </c>
-      <c r="T24">
+      <c r="T24" t="n">
         <v>13409</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
-      <c r="A25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25">
+      <c r="U24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>海口</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>2673.28208816566</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>3402.64418636157</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>4435</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>5293</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>8069</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>6641.27037704094</v>
       </c>
-      <c r="H25">
+      <c r="H25" t="n">
         <v>6512.03377018634</v>
       </c>
-      <c r="I25">
+      <c r="I25" t="n">
         <v>7342</v>
       </c>
-      <c r="J25">
+      <c r="J25" t="n">
         <v>7473</v>
       </c>
-      <c r="K25">
+      <c r="K25" t="n">
         <v>7636</v>
       </c>
-      <c r="L25">
+      <c r="L25" t="n">
         <v>8868</v>
       </c>
-      <c r="M25">
+      <c r="M25" t="n">
         <v>11694</v>
       </c>
-      <c r="N25">
+      <c r="N25" t="n">
         <v>12644.4713573582</v>
       </c>
-      <c r="O25">
+      <c r="O25" t="n">
         <v>15562</v>
       </c>
-      <c r="P25">
+      <c r="P25" t="n">
         <v>16494</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" t="n">
         <v>16400</v>
       </c>
-      <c r="R25">
+      <c r="R25" t="n">
         <v>16594</v>
       </c>
-      <c r="S25">
+      <c r="S25" t="n">
         <v>16561</v>
       </c>
-      <c r="T25">
+      <c r="T25" t="n">
         <v>12662</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
-      <c r="A26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26">
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>8848.04222323718</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>13369.6347124593</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>12823</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>14389</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>18954</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>21037.0520433648</v>
       </c>
-      <c r="H26">
+      <c r="H26" t="n">
         <v>18995.9235767374</v>
       </c>
-      <c r="I26">
+      <c r="I26" t="n">
         <v>23427</v>
       </c>
-      <c r="J26">
+      <c r="J26" t="n">
         <v>24040</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="n">
         <v>33661</v>
       </c>
-      <c r="L26">
+      <c r="L26" t="n">
         <v>45498</v>
       </c>
-      <c r="M26">
+      <c r="M26" t="n">
         <v>48622</v>
       </c>
-      <c r="N26">
+      <c r="N26" t="n">
         <v>55441.0099034991</v>
       </c>
-      <c r="O26">
+      <c r="O26" t="n">
         <v>55769</v>
       </c>
-      <c r="P26">
+      <c r="P26" t="n">
         <v>56844</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" t="n">
         <v>61601</v>
       </c>
-      <c r="R26">
+      <c r="R26" t="n">
         <v>55758</v>
       </c>
-      <c r="S26">
+      <c r="S26" t="n">
         <v>50010</v>
       </c>
-      <c r="T26">
+      <c r="T26" t="n">
         <v>47066</v>
       </c>
-    </row>
-    <row r="27" spans="1:20">
-      <c r="A27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27">
+      <c r="U26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>2005.12772073751</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>2378.10591135781</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>2630</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>3688</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>3807</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>4352.15059014841</v>
       </c>
-      <c r="H27">
+      <c r="H27" t="n">
         <v>4713.53976513146</v>
       </c>
-      <c r="I27">
+      <c r="I27" t="n">
         <v>4943</v>
       </c>
-      <c r="J27">
+      <c r="J27" t="n">
         <v>5562</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="n">
         <v>7798</v>
       </c>
-      <c r="L27">
+      <c r="L27" t="n">
         <v>7354</v>
       </c>
-      <c r="M27">
+      <c r="M27" t="n">
         <v>9738</v>
       </c>
-      <c r="N27">
+      <c r="N27" t="n">
         <v>10398.9300200276</v>
       </c>
-      <c r="O27">
+      <c r="O27" t="n">
         <v>9234</v>
       </c>
-      <c r="P27">
+      <c r="P27" t="n">
         <v>9893</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" t="n">
         <v>10517</v>
       </c>
-      <c r="R27">
+      <c r="R27" t="n">
         <v>10126</v>
       </c>
-      <c r="S27">
+      <c r="S27" t="n">
         <v>10743</v>
       </c>
-      <c r="T27">
+      <c r="T27" t="n">
         <v>11784</v>
       </c>
-    </row>
-    <row r="28" spans="1:20">
-      <c r="A28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28">
+      <c r="U27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
         <v>3976.26518647805</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>4899.64565531152</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>5244</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>6441</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>7877</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>9553.177247718009</v>
       </c>
-      <c r="H28">
+      <c r="H28" t="n">
         <v>10644.5232986592</v>
       </c>
-      <c r="I28">
+      <c r="I28" t="n">
         <v>10155</v>
       </c>
-      <c r="J28">
+      <c r="J28" t="n">
         <v>10105</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="n">
         <v>11333</v>
       </c>
-      <c r="L28">
+      <c r="L28" t="n">
         <v>11058</v>
       </c>
-      <c r="M28">
+      <c r="M28" t="n">
         <v>10547</v>
       </c>
-      <c r="N28">
+      <c r="N28" t="n">
         <v>14381.2578812092</v>
       </c>
-      <c r="O28">
+      <c r="O28" t="n">
         <v>14186</v>
       </c>
-      <c r="P28">
+      <c r="P28" t="n">
         <v>14376</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" t="n">
         <v>15286</v>
       </c>
-      <c r="R28">
+      <c r="R28" t="n">
         <v>13761</v>
       </c>
-      <c r="S28">
+      <c r="S28" t="n">
         <v>14297</v>
       </c>
-      <c r="T28">
+      <c r="T28" t="n">
         <v>14986</v>
       </c>
-    </row>
-    <row r="29" spans="1:20">
-      <c r="A29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29">
+      <c r="U28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>西宁</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
         <v>1940.32155333809</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>2313.04604024989</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>2817</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>2811</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>3196</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>3438.6019803005</v>
       </c>
-      <c r="H29">
+      <c r="H29" t="n">
         <v>4304.28669277817</v>
       </c>
-      <c r="I29">
+      <c r="I29" t="n">
         <v>4380</v>
       </c>
-      <c r="J29">
+      <c r="J29" t="n">
         <v>4807</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="n">
         <v>4602</v>
       </c>
-      <c r="L29">
+      <c r="L29" t="n">
         <v>5007</v>
       </c>
-      <c r="M29">
+      <c r="M29" t="n">
         <v>5890</v>
       </c>
-      <c r="N29">
+      <c r="N29" t="n">
         <v>6733.36335529754</v>
       </c>
-      <c r="O29">
+      <c r="O29" t="n">
         <v>8731</v>
       </c>
-      <c r="P29">
+      <c r="P29" t="n">
         <v>9847</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" t="n">
         <v>10025</v>
       </c>
-      <c r="R29">
+      <c r="R29" t="n">
         <v>9440</v>
       </c>
-      <c r="S29">
+      <c r="S29" t="n">
         <v>8925</v>
       </c>
-      <c r="T29">
+      <c r="T29" t="n">
         <v>8396</v>
       </c>
-    </row>
-    <row r="30" spans="1:20">
-      <c r="A30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30">
+      <c r="U29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
         <v>3072.82550352232</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>3215.45059794807</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>3768</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>3749</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>4341</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="n">
         <v>5829.79460172051</v>
       </c>
-      <c r="H30">
+      <c r="H30" t="n">
         <v>6224.02588998078</v>
       </c>
-      <c r="I30">
+      <c r="I30" t="n">
         <v>6435</v>
       </c>
-      <c r="J30">
+      <c r="J30" t="n">
         <v>6105</v>
       </c>
-      <c r="K30">
+      <c r="K30" t="n">
         <v>6221</v>
       </c>
-      <c r="L30">
+      <c r="L30" t="n">
         <v>6385</v>
       </c>
-      <c r="M30">
+      <c r="M30" t="n">
         <v>8166</v>
       </c>
-      <c r="N30">
+      <c r="N30" t="n">
         <v>9984.538953113761</v>
       </c>
-      <c r="O30">
+      <c r="O30" t="n">
         <v>11627</v>
       </c>
-      <c r="P30">
+      <c r="P30" t="n">
         <v>13743</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" t="n">
         <v>15221</v>
       </c>
-      <c r="R30">
+      <c r="R30" t="n">
         <v>15909</v>
       </c>
-      <c r="S30">
+      <c r="S30" t="n">
         <v>17084</v>
       </c>
-      <c r="T30">
+      <c r="T30" t="n">
         <v>15999</v>
       </c>
-    </row>
-    <row r="31" spans="1:20">
-      <c r="A31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31">
+      <c r="U30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>2137.56966961537</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>2619.40672104584</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>2866</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>3496</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>4233</v>
       </c>
-      <c r="G31">
+      <c r="G31" t="n">
         <v>4587.98395083944</v>
       </c>
-      <c r="H31">
+      <c r="H31" t="n">
         <v>4472.69474555646</v>
       </c>
-      <c r="I31">
+      <c r="I31" t="n">
         <v>4488</v>
       </c>
-      <c r="J31">
+      <c r="J31" t="n">
         <v>4904</v>
       </c>
-      <c r="K31">
+      <c r="K31" t="n">
         <v>4967</v>
       </c>
-      <c r="L31">
+      <c r="L31" t="n">
         <v>5392</v>
       </c>
-      <c r="M31">
+      <c r="M31" t="n">
         <v>6552</v>
       </c>
-      <c r="N31">
+      <c r="N31" t="n">
         <v>8842.95544974097</v>
       </c>
-      <c r="O31">
+      <c r="O31" t="n">
         <v>9799</v>
       </c>
-      <c r="P31">
+      <c r="P31" t="n">
         <v>9157</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" t="n">
         <v>9015</v>
       </c>
-      <c r="R31">
+      <c r="R31" t="n">
         <v>9271</v>
       </c>
-      <c r="S31">
+      <c r="S31" t="n">
         <v>9463</v>
       </c>
-      <c r="T31">
+      <c r="T31" t="n">
         <v>9130</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
-      <c r="A32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32">
+      <c r="U31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
         <v>2690.69348366386</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>3328.17612964796</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>3598</v>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>4057</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>4596</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="n">
         <v>4692.28948576261</v>
       </c>
-      <c r="H32">
+      <c r="H32" t="n">
         <v>5643.07047052799</v>
       </c>
-      <c r="I32">
+      <c r="I32" t="n">
         <v>6587</v>
       </c>
-      <c r="J32">
+      <c r="J32" t="n">
         <v>6579</v>
       </c>
-      <c r="K32">
+      <c r="K32" t="n">
         <v>7223</v>
       </c>
-      <c r="L32">
+      <c r="L32" t="n">
         <v>8093</v>
       </c>
-      <c r="M32">
+      <c r="M32" t="n">
         <v>8323</v>
       </c>
-      <c r="N32">
+      <c r="N32" t="n">
         <v>8155.94428623312</v>
       </c>
-      <c r="O32">
+      <c r="O32" t="n">
         <v>9332</v>
       </c>
-      <c r="P32">
+      <c r="P32" t="n">
         <v>9845</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" t="n">
         <v>9665</v>
       </c>
-      <c r="R32">
+      <c r="R32" t="n">
         <v>8048</v>
       </c>
-      <c r="S32">
+      <c r="S32" t="n">
         <v>8614</v>
       </c>
-      <c r="T32">
+      <c r="T32" t="n">
         <v>7942</v>
       </c>
-    </row>
-    <row r="33" spans="1:20">
-      <c r="A33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33">
+      <c r="U32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>2081.31120746949</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>2588.21528778998</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="n">
         <v>2640</v>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>3266</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>4040</v>
       </c>
-      <c r="G33">
+      <c r="G33" t="n">
         <v>4492.30028589685</v>
       </c>
-      <c r="H33">
+      <c r="H33" t="n">
         <v>4804.79552756257</v>
       </c>
-      <c r="I33">
+      <c r="I33" t="n">
         <v>5239</v>
       </c>
-      <c r="J33">
+      <c r="J33" t="n">
         <v>5094</v>
       </c>
-      <c r="K33">
+      <c r="K33" t="n">
         <v>5012</v>
       </c>
-      <c r="L33">
+      <c r="L33" t="n">
         <v>5162</v>
       </c>
-      <c r="M33">
+      <c r="M33" t="n">
         <v>6605</v>
       </c>
-      <c r="N33">
+      <c r="N33" t="n">
         <v>8189.97602218537</v>
       </c>
-      <c r="O33">
+      <c r="O33" t="n">
         <v>8657</v>
       </c>
-      <c r="P33">
+      <c r="P33" t="n">
         <v>8917</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" t="n">
         <v>9678</v>
       </c>
-      <c r="R33">
+      <c r="R33" t="n">
         <v>8526</v>
       </c>
-      <c r="S33">
+      <c r="S33" t="n">
         <v>8558</v>
       </c>
-      <c r="T33">
+      <c r="T33" t="n">
         <v>8243</v>
       </c>
-    </row>
-    <row r="34" spans="1:20">
-      <c r="A34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34">
+      <c r="U33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
         <v>2184.99257653053</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>2229.52688619408</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>2592</v>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>3219</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="n">
         <v>3610</v>
       </c>
-      <c r="G34">
+      <c r="G34" t="n">
         <v>3979.61769109</v>
       </c>
-      <c r="H34">
+      <c r="H34" t="n">
         <v>4187.25758662761</v>
       </c>
-      <c r="I34">
+      <c r="I34" t="n">
         <v>4524</v>
       </c>
-      <c r="J34">
+      <c r="J34" t="n">
         <v>4111</v>
       </c>
-      <c r="K34">
+      <c r="K34" t="n">
         <v>4498</v>
       </c>
-      <c r="L34">
+      <c r="L34" t="n">
         <v>4448</v>
       </c>
-      <c r="M34">
+      <c r="M34" t="n">
         <v>4892</v>
       </c>
-      <c r="N34">
+      <c r="N34" t="n">
         <v>5589.49274177867</v>
       </c>
-      <c r="O34">
+      <c r="O34" t="n">
         <v>6440</v>
       </c>
-      <c r="P34">
+      <c r="P34" t="n">
         <v>7353</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" t="n">
         <v>8143</v>
       </c>
-      <c r="R34">
+      <c r="R34" t="n">
         <v>8410</v>
       </c>
-      <c r="S34">
+      <c r="S34" t="n">
         <v>8509</v>
       </c>
-      <c r="T34">
+      <c r="T34" t="n">
         <v>8272</v>
       </c>
-    </row>
-    <row r="35" spans="1:20">
-      <c r="A35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35">
+      <c r="U34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
         <v>2408.02783160377</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>3118.30223495624</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>3344</v>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>4012</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="n">
         <v>5097</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="n">
         <v>5969.66093088111</v>
       </c>
-      <c r="H35">
+      <c r="H35" t="n">
         <v>5273.35010761815</v>
       </c>
-      <c r="I35">
+      <c r="I35" t="n">
         <v>5729</v>
       </c>
-      <c r="J35">
+      <c r="J35" t="n">
         <v>5847</v>
       </c>
-      <c r="K35">
+      <c r="K35" t="n">
         <v>6374</v>
       </c>
-      <c r="L35">
+      <c r="L35" t="n">
         <v>6018</v>
       </c>
-      <c r="M35">
+      <c r="M35" t="n">
         <v>6811</v>
       </c>
-      <c r="N35">
+      <c r="N35" t="n">
         <v>8091.84553824634</v>
       </c>
-      <c r="O35">
+      <c r="O35" t="n">
         <v>8731</v>
       </c>
-      <c r="P35">
+      <c r="P35" t="n">
         <v>9128</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" t="n">
         <v>8506</v>
       </c>
-      <c r="R35">
+      <c r="R35" t="n">
         <v>8799</v>
       </c>
-      <c r="S35">
+      <c r="S35" t="n">
         <v>8300</v>
       </c>
-      <c r="T35">
+      <c r="T35" t="n">
         <v>7812</v>
       </c>
-    </row>
-    <row r="36" spans="1:20">
-      <c r="A36" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36">
+      <c r="U35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
         <v>2430.68122159859</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>3191.02400979804</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>3165</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>3533</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>4322</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="n">
         <v>5481.49083785697</v>
       </c>
-      <c r="H36">
+      <c r="H36" t="n">
         <v>5602.51111505081</v>
       </c>
-      <c r="I36">
+      <c r="I36" t="n">
         <v>5759</v>
       </c>
-      <c r="J36">
+      <c r="J36" t="n">
         <v>5458</v>
       </c>
-      <c r="K36">
+      <c r="K36" t="n">
         <v>5544</v>
       </c>
-      <c r="L36">
+      <c r="L36" t="n">
         <v>6160</v>
       </c>
-      <c r="M36">
+      <c r="M36" t="n">
         <v>7287</v>
       </c>
-      <c r="N36">
+      <c r="N36" t="n">
         <v>7796.1980582912</v>
       </c>
-      <c r="O36">
+      <c r="O36" t="n">
         <v>8227</v>
       </c>
-      <c r="P36">
+      <c r="P36" t="n">
         <v>9112</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" t="n">
         <v>10119</v>
       </c>
-      <c r="R36">
+      <c r="R36" t="n">
         <v>10703</v>
       </c>
-      <c r="S36">
+      <c r="S36" t="n">
         <v>11239</v>
       </c>
-      <c r="T36">
+      <c r="T36" t="n">
         <v>9997</v>
       </c>
-    </row>
-    <row r="37" spans="1:20">
-      <c r="A37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37">
+      <c r="U36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>4000.92307086484</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>5104.94042082179</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="n">
         <v>4788</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>5383</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>6421</v>
       </c>
-      <c r="G37">
+      <c r="G37" t="n">
         <v>7166.1854785709</v>
       </c>
-      <c r="H37">
+      <c r="H37" t="n">
         <v>7583.35748769908</v>
       </c>
-      <c r="I37">
+      <c r="I37" t="n">
         <v>7987</v>
       </c>
-      <c r="J37">
+      <c r="J37" t="n">
         <v>7855</v>
       </c>
-      <c r="K37">
+      <c r="K37" t="n">
         <v>8437</v>
       </c>
-      <c r="L37">
+      <c r="L37" t="n">
         <v>8997</v>
       </c>
-      <c r="M37">
+      <c r="M37" t="n">
         <v>10052</v>
       </c>
-      <c r="N37">
+      <c r="N37" t="n">
         <v>12373.4398931918</v>
       </c>
-      <c r="O37">
+      <c r="O37" t="n">
         <v>13674</v>
       </c>
-      <c r="P37">
+      <c r="P37" t="n">
         <v>14058</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" t="n">
         <v>14365</v>
       </c>
-      <c r="R37">
+      <c r="R37" t="n">
         <v>14440</v>
       </c>
-      <c r="S37">
+      <c r="S37" t="n">
         <v>13952</v>
       </c>
-      <c r="T37">
+      <c r="T37" t="n">
         <v>14554</v>
       </c>
+      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>